--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,26 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jayis\Projects\1DOF-FOC-Force-Feedback\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCDDA29-52BA-4F2F-9016-E3C51CE8E703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>DigiKey</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/stmicroelectronics/B-G431B-ESC1/10321670</t>
+  </si>
+  <si>
+    <t>Magnetic Encoder</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/ams-osram-usa-inc/AS5047P-ADAPTERBOARD/5452344</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>RCTimer</t>
+  </si>
+  <si>
+    <t>https://www.rctimer.com/rctimer-gbm2804-hollow-shaft-brushless-gimbal-motor-p0445.html</t>
+  </si>
+  <si>
+    <t>USB-CAN Adapter</t>
+  </si>
+  <si>
+    <t>ODrive</t>
+  </si>
+  <si>
+    <t>https://shop.odriverobotics.com/products/usb-can-adapter</t>
+  </si>
+  <si>
+    <t>Magnets</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/radial-magnets-inc/8995/5126077</t>
+  </si>
+  <si>
+    <t>12V Power Supply</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Towisituati-100V-240V-Converter-Transformer-Connector/dp/B0F4X4J3SL/ref=sr_1_6?crid=2540MOC58HED1&amp;dib=eyJ2IjoiMSJ9.PYWD828vV2b5kV5LnpTZBeF6XqCTnRbYqKlC4v680_OXOOi0p44urKCjc_Y0GJ1tJfakL-ceRcGHOxu_84mRdzvDY8frX-CuSdalss393g7QWGPPzqiASbKtCapaNrzmtGAH0d7nsO9QOHstRhykyclJSZ9fzbk3T5Sp3EjnL2tm1SBikvxV42LBFBbCrYdmkPV9hMeIFupXLco3_FFEZA-SPqInSktBDW78O8kCbaA.AadlrM6WTfXi9kMbDy1qXMCagpHDnCZPLpAh01uOpf8&amp;dib_tag=se&amp;keywords=12v+power+supply+with+terminals&amp;qid=1779682028&amp;sprefix=12v+power+supply+wi%2Caps%2C111&amp;sr=8-6#customerReviews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff Estimate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping </t>
+  </si>
+  <si>
+    <t>Shipping + Tariff</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +113,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -45,14 +168,239 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF284E3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +678,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5">
+        <v>39.53</v>
+      </c>
+      <c r="F1" s="6">
+        <f>D1*E1</f>
+        <v>79.06</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="10">
+        <v>2</v>
+      </c>
+      <c r="E2" s="11">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="F2" s="6">
+        <f t="shared" ref="F2:F10" si="0">D2*E2</f>
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>10.94</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" si="0"/>
+        <v>32.82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11">
+        <v>37</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4">
+        <v>10</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13">
+        <v>20</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16">
+        <v>18.71</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="0"/>
+        <v>18.71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17">
+        <v>1</v>
+      </c>
+      <c r="E8" s="18">
+        <v>6.99</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13">
+        <f>10.83+3.7</f>
+        <v>14.530000000000001</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="0"/>
+        <v>14.530000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21">
+        <v>1</v>
+      </c>
+      <c r="E10" s="22">
+        <v>17</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="25">
+        <f>SUM(F1:F10)</f>
+        <v>268.21000000000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" xr:uid="{DE81C74D-39DA-44B8-9B02-BC70964207B3}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{68173086-9C2C-464B-BC9F-B4049250A5D5}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{EF06FAB2-E561-4A38-879B-49B58CCD194E}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{62715946-B9F2-452F-A822-308EB3792819}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{AE3BA2FD-EADF-4525-9F8D-B1661B189940}"/>
+    <hyperlink ref="C6" r:id="rId6" location="customerReviews" display="https://www.amazon.com/Towisituati-100V-240V-Converter-Transformer-Connector/dp/B0F4X4J3SL/ref=sr_1_6?crid=2540MOC58HED1&amp;dib=eyJ2IjoiMSJ9.PYWD828vV2b5kV5LnpTZBeF6XqCTnRbYqKlC4v680_OXOOi0p44urKCjc_Y0GJ1tJfakL-ceRcGHOxu_84mRdzvDY8frX-CuSdalss393g7QWGPPzqiASbKtCapaNrzmtGAH0d7nsO9QOHstRhykyclJSZ9fzbk3T5Sp3EjnL2tm1SBikvxV42LBFBbCrYdmkPV9hMeIFupXLco3_FFEZA-SPqInSktBDW78O8kCbaA.AadlrM6WTfXi9kMbDy1qXMCagpHDnCZPLpAh01uOpf8&amp;dib_tag=se&amp;keywords=12v+power+supply+with+terminals&amp;qid=1779682028&amp;sprefix=12v+power+supply+wi%2Caps%2C111&amp;sr=8-6#customerReviews" xr:uid="{9735080A-9B61-4143-B5C9-9A168F6FD298}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>